--- a/backtest_runs/20260410_193731/by_symbol/SYS/SYS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SYS/SYS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-5022.849999999996</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98346.81</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98346.81</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>106786.78</v>
@@ -1047,7 +1047,7 @@
         <v>-450.8699999999946</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>109982.42</v>
@@ -1185,7 +1185,7 @@
         <v>-2879.239999999989</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>118825.8</v>
@@ -1277,7 +1277,7 @@
         <v>-3045.350000000018</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>117908.24</v>
@@ -1415,7 +1415,7 @@
         <v>-2895.059999999997</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>120589.73</v>
@@ -1461,7 +1461,7 @@
         <v>-3045.349999999995</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>117544.38</v>
@@ -1645,7 +1645,7 @@
         <v>-2475.829999999996</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>129535.94</v>
